--- a/design/numbers/gameplay-numbers.xlsx
+++ b/design/numbers/gameplay-numbers.xlsx
@@ -5396,7 +5396,7 @@
         <v>entity.monster.cbe1f18ad64d8183</v>
       </c>
       <c r="B250" t="str">
-        <v>你看到:</v>
+        <v>沙漠蝎王</v>
       </c>
       <c r="C250">
         <v>124</v>
@@ -5736,7 +5736,7 @@
         <v>entity.monster.ee31f5f9df972310</v>
       </c>
       <c r="B267" t="str">
-        <v>你看到:</v>
+        <v>吞兽</v>
       </c>
       <c r="C267">
         <v>118</v>
@@ -5756,7 +5756,7 @@
         <v>entity.monster.e9a94e35bb84c0dd</v>
       </c>
       <c r="B268" t="str">
-        <v>你看到:</v>
+        <v>落日蛮牛</v>
       </c>
       <c r="C268">
         <v>54</v>
@@ -63739,8 +63739,8 @@
       <c r="C29" t="str">
         <v>+天魔荆棘皇冠</v>
       </c>
-      <c r="D29" t="str">
-        <v/>
+      <c r="D29">
+        <v>125</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -63768,8 +63768,8 @@
       <c r="C30" t="str">
         <v>+天魔玄夜战铠</v>
       </c>
-      <c r="D30" t="str">
-        <v/>
+      <c r="D30">
+        <v>140</v>
       </c>
       <c r="E30" t="str">
         <v/>
